--- a/research/traditional_assets/database/data/austria/austria_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/austria/austria_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,7 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.105</v>
+        <v>-0.08210000000000001</v>
+      </c>
+      <c r="E2">
+        <v>-0.248</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -597,16 +600,16 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-0.06067935573135062</v>
+        <v>0.01273632145876745</v>
       </c>
       <c r="J2">
-        <v>-0.06067935573135062</v>
+        <v>0.009393595686431293</v>
       </c>
       <c r="K2">
-        <v>-7.19</v>
+        <v>1.92</v>
       </c>
       <c r="L2">
-        <v>-0.4696276943174396</v>
+        <v>0.09846153846153846</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,67 +627,73 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.051</v>
+        <v>0.047</v>
       </c>
       <c r="V2">
-        <v>0.001398409651768577</v>
+        <v>0.001649122807017544</v>
+      </c>
+      <c r="W2">
+        <v>0.04033613445378151</v>
       </c>
       <c r="X2">
-        <v>0.07304762912038613</v>
+        <v>0.1472561193742875</v>
+      </c>
+      <c r="Y2">
+        <v>-0.106919984920506</v>
       </c>
       <c r="Z2">
-        <v>0.1332149919199956</v>
+        <v>0.1697316892613106</v>
+      </c>
+      <c r="AA2">
+        <v>0.001594390864095744</v>
       </c>
       <c r="AB2">
-        <v>0.04567697160026205</v>
+        <v>0.07679596779333664</v>
+      </c>
+      <c r="AC2">
+        <v>-0.0752015769292409</v>
       </c>
       <c r="AD2">
-        <v>65.09999999999999</v>
+        <v>68</v>
       </c>
       <c r="AE2">
-        <v>3.175004681234891</v>
+        <v>2.728208657770173</v>
       </c>
       <c r="AF2">
-        <v>68.27500468123489</v>
+        <v>70.72820865777017</v>
       </c>
       <c r="AG2">
-        <v>68.22400468123489</v>
+        <v>70.68120865777017</v>
       </c>
       <c r="AH2">
-        <v>0.6518211048728549</v>
+        <v>0.7127832862699948</v>
       </c>
       <c r="AI2">
-        <v>0.5841711396499899</v>
+        <v>0.6143429962331531</v>
       </c>
       <c r="AJ2">
-        <v>0.6516514951258064</v>
+        <v>0.7126471799880892</v>
       </c>
       <c r="AK2">
-        <v>0.583989607849777</v>
+        <v>0.6141854911166494</v>
       </c>
       <c r="AL2">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="AN2">
-        <v>76.95035460992908</v>
-      </c>
-      <c r="AO2">
-        <v>-1.583333333333333</v>
+        <v>85.64231738035264</v>
       </c>
       <c r="AP2">
-        <v>80.6430315381027</v>
-      </c>
-      <c r="AQ2">
-        <v>-1.583333333333333</v>
+        <v>89.01915448081886</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.105</v>
+        <v>-0.08210000000000001</v>
+      </c>
+      <c r="E3">
+        <v>-0.248</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -713,16 +725,16 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.01715439542707494</v>
+        <v>0.01273632145876745</v>
       </c>
       <c r="J3">
-        <v>0.01715439542707494</v>
+        <v>0.009393595686431293</v>
       </c>
       <c r="K3">
-        <v>-5.54</v>
+        <v>1.92</v>
       </c>
       <c r="L3">
-        <v>-0.4504065040650406</v>
+        <v>0.09846153846153846</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -731,7 +743,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -740,61 +752,61 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.051</v>
+        <v>0.047</v>
       </c>
       <c r="V3">
-        <v>0.001661237785016287</v>
+        <v>0.001649122807017544</v>
       </c>
       <c r="W3">
-        <v>-0.1108</v>
+        <v>0.04033613445378151</v>
       </c>
       <c r="X3">
-        <v>0.09939857229254047</v>
+        <v>0.1472561193742875</v>
       </c>
       <c r="Y3">
-        <v>-0.2101985722925405</v>
+        <v>-0.106919984920506</v>
       </c>
       <c r="Z3">
-        <v>0.107024454645065</v>
+        <v>0.1697316892613106</v>
       </c>
       <c r="AA3">
-        <v>0.001835939815348493</v>
+        <v>0.001594390864095744</v>
       </c>
       <c r="AB3">
-        <v>0.0446572572522923</v>
+        <v>0.07679596779333664</v>
       </c>
       <c r="AC3">
-        <v>-0.04282131743694381</v>
+        <v>-0.0752015769292409</v>
       </c>
       <c r="AD3">
-        <v>65.09999999999999</v>
+        <v>68</v>
       </c>
       <c r="AE3">
-        <v>3.175004681234891</v>
+        <v>2.728208657770173</v>
       </c>
       <c r="AF3">
-        <v>68.27500468123489</v>
+        <v>70.72820865777017</v>
       </c>
       <c r="AG3">
-        <v>68.22400468123489</v>
+        <v>70.68120865777017</v>
       </c>
       <c r="AH3">
-        <v>0.6898206764538749</v>
+        <v>0.7127832862699948</v>
       </c>
       <c r="AI3">
-        <v>0.5841711396499899</v>
+        <v>0.6143429962331531</v>
       </c>
       <c r="AJ3">
-        <v>0.6896607643521375</v>
+        <v>0.7126471799880892</v>
       </c>
       <c r="AK3">
-        <v>0.583989607849777</v>
+        <v>0.6141854911166494</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -803,108 +815,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>76.95035460992908</v>
+        <v>85.64231738035264</v>
       </c>
       <c r="AP3">
-        <v>80.6430315381027</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Austria</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>startup300 AG (WBAG:S300)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>-0.3787375415282392</v>
-      </c>
-      <c r="J4">
-        <v>-0.3787375415282392</v>
-      </c>
-      <c r="K4">
-        <v>-1.65</v>
-      </c>
-      <c r="L4">
-        <v>-0.5481727574750831</v>
-      </c>
-      <c r="M4">
-        <v>-0</v>
-      </c>
-      <c r="N4">
-        <v>-0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>-0</v>
-      </c>
-      <c r="Q4">
-        <v>-0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="X4">
-        <v>0.0466966859482318</v>
-      </c>
-      <c r="AB4">
-        <v>0.0466966859482318</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <v>0</v>
-      </c>
-      <c r="AH4">
-        <v>0</v>
-      </c>
-      <c r="AJ4">
-        <v>0</v>
-      </c>
-      <c r="AL4">
-        <v>0.72</v>
-      </c>
-      <c r="AM4">
-        <v>0.72</v>
-      </c>
-      <c r="AO4">
-        <v>-1.583333333333333</v>
-      </c>
-      <c r="AQ4">
-        <v>-1.583333333333333</v>
+        <v>89.01915448081886</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/austria/austria_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/austria/austria_investments_asset_management.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.08210000000000001</v>
+        <v>-0.124</v>
       </c>
       <c r="E2">
-        <v>-0.248</v>
+        <v>-0.26</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,88 +600,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.01273632145876745</v>
+        <v>0.01061235402537352</v>
       </c>
       <c r="J2">
-        <v>0.009393595686431293</v>
+        <v>0.007401000402464899</v>
       </c>
       <c r="K2">
-        <v>1.92</v>
+        <v>3.47</v>
       </c>
       <c r="L2">
-        <v>0.09846153846153846</v>
+        <v>0.1549107142857143</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.04581939799331104</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.3948126801152738</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.04581939799331104</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.3948126801152738</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>0.047</v>
+        <v>0.034</v>
       </c>
       <c r="V2">
-        <v>0.001649122807017544</v>
+        <v>0.001137123745819398</v>
       </c>
       <c r="W2">
-        <v>0.04033613445378151</v>
+        <v>0.07977011494252874</v>
       </c>
       <c r="X2">
-        <v>0.1472561193742875</v>
+        <v>0.1034305057147172</v>
       </c>
       <c r="Y2">
-        <v>-0.106919984920506</v>
+        <v>-0.02366039077218843</v>
       </c>
       <c r="Z2">
-        <v>0.1697316892613106</v>
+        <v>0.1969275498200428</v>
       </c>
       <c r="AA2">
-        <v>0.001594390864095744</v>
+        <v>0.001457460875474563</v>
       </c>
       <c r="AB2">
-        <v>0.07679596779333664</v>
+        <v>0.06452819477027136</v>
       </c>
       <c r="AC2">
-        <v>-0.0752015769292409</v>
+        <v>-0.0630707338947968</v>
       </c>
       <c r="AD2">
-        <v>68</v>
+        <v>53.9</v>
       </c>
       <c r="AE2">
-        <v>2.728208657770173</v>
+        <v>2.726416349158166</v>
       </c>
       <c r="AF2">
-        <v>70.72820865777017</v>
+        <v>56.62641634915816</v>
       </c>
       <c r="AG2">
-        <v>70.68120865777017</v>
+        <v>56.59241634915816</v>
       </c>
       <c r="AH2">
-        <v>0.7127832862699948</v>
+        <v>0.6544407908985255</v>
       </c>
       <c r="AI2">
-        <v>0.6143429962331531</v>
+        <v>0.5422614155389874</v>
       </c>
       <c r="AJ2">
-        <v>0.7126471799880892</v>
+        <v>0.6543049522480936</v>
       </c>
       <c r="AK2">
-        <v>0.6141854911166494</v>
+        <v>0.5421123327567705</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -690,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>85.64231738035264</v>
+        <v>68.83780332056193</v>
       </c>
       <c r="AP2">
-        <v>89.01915448081886</v>
+        <v>72.2763938047997</v>
       </c>
     </row>
     <row r="3">
@@ -713,10 +716,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.08210000000000001</v>
+        <v>-0.124</v>
       </c>
       <c r="E3">
-        <v>-0.248</v>
+        <v>-0.26</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -725,88 +728,91 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.01273632145876745</v>
+        <v>0.01061235402537352</v>
       </c>
       <c r="J3">
-        <v>0.009393595686431293</v>
+        <v>0.007401000402464899</v>
       </c>
       <c r="K3">
-        <v>1.92</v>
+        <v>3.47</v>
       </c>
       <c r="L3">
-        <v>0.09846153846153846</v>
+        <v>0.1549107142857143</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>1.37</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.04581939799331104</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.3948126801152738</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>1.37</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.04581939799331104</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.3948126801152738</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>0.047</v>
+        <v>0.034</v>
       </c>
       <c r="V3">
-        <v>0.001649122807017544</v>
+        <v>0.001137123745819398</v>
       </c>
       <c r="W3">
-        <v>0.04033613445378151</v>
+        <v>0.07977011494252874</v>
       </c>
       <c r="X3">
-        <v>0.1472561193742875</v>
+        <v>0.1034305057147172</v>
       </c>
       <c r="Y3">
-        <v>-0.106919984920506</v>
+        <v>-0.02366039077218843</v>
       </c>
       <c r="Z3">
-        <v>0.1697316892613106</v>
+        <v>0.1969275498200428</v>
       </c>
       <c r="AA3">
-        <v>0.001594390864095744</v>
+        <v>0.001457460875474563</v>
       </c>
       <c r="AB3">
-        <v>0.07679596779333664</v>
+        <v>0.06452819477027136</v>
       </c>
       <c r="AC3">
-        <v>-0.0752015769292409</v>
+        <v>-0.0630707338947968</v>
       </c>
       <c r="AD3">
-        <v>68</v>
+        <v>53.9</v>
       </c>
       <c r="AE3">
-        <v>2.728208657770173</v>
+        <v>2.726416349158166</v>
       </c>
       <c r="AF3">
-        <v>70.72820865777017</v>
+        <v>56.62641634915816</v>
       </c>
       <c r="AG3">
-        <v>70.68120865777017</v>
+        <v>56.59241634915816</v>
       </c>
       <c r="AH3">
-        <v>0.7127832862699948</v>
+        <v>0.6544407908985255</v>
       </c>
       <c r="AI3">
-        <v>0.6143429962331531</v>
+        <v>0.5422614155389874</v>
       </c>
       <c r="AJ3">
-        <v>0.7126471799880892</v>
+        <v>0.6543049522480936</v>
       </c>
       <c r="AK3">
-        <v>0.6141854911166494</v>
+        <v>0.5421123327567705</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -815,10 +821,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>85.64231738035264</v>
+        <v>68.83780332056193</v>
       </c>
       <c r="AP3">
-        <v>89.01915448081886</v>
+        <v>72.2763938047997</v>
       </c>
     </row>
   </sheetData>
